--- a/per-stock/MDB/financials.xlsx
+++ b/per-stock/MDB/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26253445120</v>
+        <v>26763724800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23886503936</v>
+        <v>24395206656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46.046715</v>
+        <v>45.34435</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.655685</v>
+        <v>10.284251</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -608,7 +617,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.71749</v>
+        <v>0.71970004</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -623,7 +632,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.00044</v>
+        <v>-0.03607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -638,7 +647,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.02888</v>
+        <v>-0.01118</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -653,7 +662,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.02481</v>
+        <v>-0.00975</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -668,7 +677,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.267</v>
+        <v>0.252</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -683,7 +692,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2387240960</v>
+        <v>2427152896</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -698,7 +707,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>62831000</v>
+        <v>58635000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>463322496</v>
+        <v>591182000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -728,7 +737,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>80499934</v>
+        <v>80431927</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>326.13</v>
+        <v>332.75</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B42:E42)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D40</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C40</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B40</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B40:E40)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D33</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C33</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B33</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B33:E33)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D8</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C8</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B8:E8)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B5:E5)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1632,7 +2112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1657,27 +2137,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
         </is>
       </c>
     </row>
@@ -1710,10 +2190,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.199608</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.21</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0.21</v>
@@ -1732,19 +2212,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>18774000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>28470000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>11713000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-32136000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-23198000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>11901000</v>
       </c>
     </row>
     <row r="5">
@@ -1754,19 +2234,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>15530000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-2007000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-47048000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-37626000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>15826000</v>
       </c>
     </row>
     <row r="6">
@@ -1776,19 +2256,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>9127000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>9279000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>9562000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>9511000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>9060000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>6112000</v>
       </c>
     </row>
     <row r="7">
@@ -1798,19 +2278,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>191441000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>187412000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>179177000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>171428000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>158041000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>149015000</v>
       </c>
     </row>
     <row r="8">
@@ -1820,19 +2300,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>18774000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>28470000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>11713000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>-32136000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>-23198000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>11901000</v>
       </c>
     </row>
     <row r="9">
@@ -1842,19 +2322,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>9647000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>19191000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>2151000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>-41647000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>-32258000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>5789000</v>
       </c>
     </row>
     <row r="10">
@@ -1864,19 +2344,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>18498000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>20550000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>20359000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>22164000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>22392000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>22812000</v>
       </c>
     </row>
     <row r="11">
@@ -1886,19 +2366,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>853000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-212000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>801000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>1473000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>1066000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1635000</v>
       </c>
     </row>
     <row r="12">
@@ -1908,19 +2388,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>19351000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>20338000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>21160000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>23637000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>23458000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>24447000</v>
       </c>
     </row>
     <row r="13">
@@ -1930,19 +2410,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>15530000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-2007000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-47048000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-37626000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>15826000</v>
       </c>
     </row>
     <row r="14">
@@ -1952,19 +2432,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>15530000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-2007000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-47048000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-37626000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>15826000</v>
       </c>
     </row>
     <row r="15">
@@ -1974,19 +2454,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>712420000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>694768000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>646733000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>656696000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>602568000</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>566960000</v>
       </c>
     </row>
     <row r="16">
@@ -1996,19 +2476,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-24804000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>304000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-18424000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-65294000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-53554000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>-18562000</v>
       </c>
     </row>
     <row r="17">
@@ -2018,19 +2498,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>81581387</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>86457703</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>81401853</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>81078234</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>81060822</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>84594079</v>
       </c>
     </row>
     <row r="18">
@@ -2040,19 +2520,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>80357498</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>81281748</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>81401853</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>81078234</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>81060822</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>77631824</v>
       </c>
     </row>
     <row r="19">
@@ -2062,19 +2542,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>0.18</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-0.58</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-0.46</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0.19</v>
       </c>
     </row>
     <row r="20">
@@ -2084,19 +2564,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.19</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-0.58</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-0.46</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="21">
@@ -2106,19 +2586,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>15530000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-2007000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-47048000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-37626000</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>15826000</v>
       </c>
     </row>
     <row r="22">
@@ -2128,19 +2608,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>15530000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-2007000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-47048000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-37626000</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>15826000</v>
       </c>
     </row>
     <row r="23">
@@ -2150,19 +2630,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>15530000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-2007000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-47048000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-37626000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>15826000</v>
       </c>
     </row>
     <row r="24">
@@ -2172,19 +2652,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>15530000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-2007000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-47048000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-37626000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>15826000</v>
       </c>
     </row>
     <row r="25">
@@ -2194,19 +2674,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>15530000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-2007000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-47048000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-37626000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>15826000</v>
       </c>
     </row>
     <row r="26">
@@ -2216,19 +2696,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>4360000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>3873000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>3357000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>3928000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>4302000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-11672000</v>
       </c>
     </row>
     <row r="27">
@@ -2238,19 +2718,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>8794000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>19403000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>1350000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-43120000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-33324000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>4154000</v>
       </c>
     </row>
     <row r="28">
@@ -2260,19 +2740,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>15100000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-1451000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-585000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-2162000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>-96000</v>
       </c>
     </row>
     <row r="29">
@@ -2282,19 +2762,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>15100000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-1451000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-585000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-2162000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-96000</v>
       </c>
     </row>
     <row r="30">
@@ -2304,19 +2784,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>18498000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>20550000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>20359000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>22164000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>22392000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>22812000</v>
       </c>
     </row>
     <row r="31">
@@ -2326,19 +2806,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>853000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-212000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>801000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>1473000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>1066000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>1635000</v>
       </c>
     </row>
     <row r="32">
@@ -2348,19 +2828,19 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>19351000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>20338000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>21160000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>23637000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>23458000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>24447000</v>
       </c>
     </row>
     <row r="33">
@@ -2370,19 +2850,19 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-24804000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>304000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-18424000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-65294000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-53554000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>-18562000</v>
       </c>
     </row>
     <row r="34">
@@ -2392,19 +2872,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>520979000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>507356000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>467556000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>485268000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>444527000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>417945000</v>
       </c>
     </row>
     <row r="35">
@@ -2414,19 +2894,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>200409000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>189125000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>176610000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>181739000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>168829000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>150400000</v>
       </c>
     </row>
     <row r="36">
@@ -2436,19 +2916,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>320570000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>318231000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>290946000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>303529000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>275698000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>267545000</v>
       </c>
     </row>
     <row r="37">
@@ -2458,19 +2938,19 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>249334000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>248537000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>230864000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>244065000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>220923000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>212211000</v>
       </c>
     </row>
     <row r="38">
@@ -2480,19 +2960,19 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>71236000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>69694000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>60082000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>59464000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>54775000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>55334000</v>
       </c>
     </row>
     <row r="39">
@@ -2502,19 +2982,19 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>71236000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>69694000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>60082000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>59464000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>54775000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>55334000</v>
       </c>
     </row>
     <row r="40">
@@ -2524,19 +3004,19 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>496175000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>507660000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>449132000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>419974000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>390973000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>399383000</v>
       </c>
     </row>
     <row r="41">
@@ -2546,19 +3026,19 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>191441000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>187412000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>179177000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>171428000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>158041000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>149015000</v>
       </c>
     </row>
     <row r="42">
@@ -2568,19 +3048,19 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>687616000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>695072000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>628309000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>591402000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>549014000</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>548398000</v>
       </c>
     </row>
     <row r="43">
@@ -2590,19 +3070,19 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>687616000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>695072000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>628309000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>591402000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>549014000</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>548398000</v>
       </c>
     </row>
   </sheetData>
@@ -2610,7 +3090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4008,7 +4488,1627 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>199912</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>2877995</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1562510</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1029045</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>99371</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>80503576</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>80492774</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>81357418</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>81546068</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>81715778</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>80703488</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>83370769</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>82919928</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>82575113</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>81815149</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n">
+        <v>451666000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>30427000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>32859000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>34625000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>35744000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2712712000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2726459000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2660490000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2711220000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2797390000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2934960000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2952358000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2888439000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2942974000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>3032950000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2441439000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2445359000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2374281000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2394706000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2467532000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2712712000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2726459000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2660490000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2711220000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2797390000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>30427000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>32859000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>34625000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>35744000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2934960000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2952358000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2888439000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2942974000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>3032950000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2934960000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2952358000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2888439000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2942974000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>3032950000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2934960000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2952358000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2888439000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2942974000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>3032950000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2934960000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2952358000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2888439000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2942974000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>3032950000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>7268000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>13207000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>10275000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>5581000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>13015000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>7268000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>13207000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>10275000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>5581000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>13015000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>8283000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>494569000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>346654000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>201341000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1319000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-1907421000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-1911855000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-1927385000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-1925378000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-1878330000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>4843315000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>5345494000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>5152122000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>5064031000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>4899504000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>81000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>81000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>81000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>81000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>81000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>81000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>81000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>81000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>757731000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>806490000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>678210000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>599087000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>591470000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>139552000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>136994000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>120177000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>89254000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>86472000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>26891000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>29454000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>27964000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>29037000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>33482000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>91594000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>83940000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>66733000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>33981000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>24904000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>91236000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>83588000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>66173000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>33274000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>24327000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>358000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>352000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>560000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>707000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>577000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>21067000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>23600000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>25480000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>26236000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>28086000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>21067000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>23600000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>25480000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>26236000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>28086000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>618179000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>669496000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>558033000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>509833000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>504998000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>341076000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>387119000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>300873000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>275877000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>295735000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>341076000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>387119000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>300873000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>275877000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>295735000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>9360000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>9259000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>9145000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>9508000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>8914000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>9360000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>9259000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>9145000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>9508000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>8914000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n">
+        <v>1124720000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n">
+        <v>1124720000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>115563000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>143046000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>131760000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>110916000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>102725000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>152180000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>130072000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>116255000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>113532000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>97624000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>110516000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>109803000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>101444000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>103664000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>89062000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>41664000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>20269000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>14811000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>9868000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>8562000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>41664000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>20269000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>14811000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>9868000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>8562000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>3692691000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>3758848000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>3566649000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>3542061000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>3624420000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>633073000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>643993000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>634335000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>637522000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>651890000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>317258000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>323322000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>311756000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>308869000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>316500000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>26061000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>26021000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>23012000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>23542000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>22410000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>26061000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>26021000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>23012000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>23542000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>22410000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>222248000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>225899000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>227949000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>231754000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>235560000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>30851000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>34502000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>38308000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>42113000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>45919000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>191397000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>191397000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>189641000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>189641000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>189641000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>67506000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>68751000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>71618000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>73357000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>77420000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n">
+        <v>-36746000</v>
+      </c>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>-30079000</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>67506000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>105497000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>71618000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>73357000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>77420000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n">
+        <v>44384000</v>
+      </c>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>41273000</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n">
+        <v>705000</v>
+      </c>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n">
+        <v>386000</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>67506000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>44544000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>71618000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>73357000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>77420000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n">
+        <v>15864000</v>
+      </c>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n">
+        <v>15257000</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>3059618000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>3114855000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>2932314000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>2904539000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>2972530000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>115277000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>97170000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>87177000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>89086000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>129894000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>131442000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>122882000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>119597000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>116291000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>387294000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>499002000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>416494000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>349656000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>313215000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>387294000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>499002000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>416494000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>349656000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>313215000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>-12252000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>-12979000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>-12305000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>-11151000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>-9893000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>399546000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>511981000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>428799000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>360807000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>323108000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>2427153000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>2387241000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>2305761000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>2345386000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>2453938000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1390799000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1303701000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1471669000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>1698247000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1796129000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>1036354000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>1083540000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>834092000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>647139000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>657809000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5200,13 +7300,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5216,6 +7316,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5226,30 +7327,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5262,21 +7368,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>199312000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>178470000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>141832000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>71568000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>108318000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>24559000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5285,17 +7392,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-100255000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-57254000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-148633000</v>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n">
+      <c r="E3" s="3" t="n">
+        <v>-194446000</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5304,21 +7416,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-1764000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-1739000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-1715000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-1691000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-2394000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-1645000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5327,21 +7440,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-2319000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-1134000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-1678000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-537000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-1611000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-25979000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5350,21 +7464,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>414000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>438000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>463000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>486000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>510000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>469000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5372,22 +7487,23 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n">
+      <c r="B7" s="3" t="n">
+        <v>3837000</v>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n">
         <v>187000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>6558000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>3899000</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="G7" s="3" t="n">
         <v>3273000</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>6576000</v>
-      </c>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5396,21 +7512,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>1039760000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>1086625000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>837170000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>650206000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>660438000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>492753000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5419,21 +7536,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1086625000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>837170000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>650206000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>660438000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>492753000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>675663000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5442,21 +7560,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-1698000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>3497000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>783000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>68000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-2876000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5465,21 +7584,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-45167000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>245958000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>186181000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-10300000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>159685000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-180034000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5488,21 +7608,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-159875000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-100303000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-188311000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-172010000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-1815000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>15744000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5511,21 +7632,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-159875000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-100303000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-188311000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-172010000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-1815000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>15744000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5534,15 +7656,18 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-58317000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-60078000</v>
       </c>
-      <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n">
         <v>-366000</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="H14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5553,21 +7678,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>461000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>18768000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>533000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>24127000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>579000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>17755000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5576,17 +7702,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-100255000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-57254000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-148633000</v>
       </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n">
+      <c r="E16" s="3" t="n">
+        <v>-194446000</v>
+      </c>
+      <c r="F16" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5595,17 +7726,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-100255000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-57254000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-148633000</v>
       </c>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n">
+      <c r="E17" s="3" t="n">
+        <v>-194446000</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5614,21 +7750,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-1764000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-1739000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-1715000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-1691000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-2394000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-1645000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5637,21 +7774,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-1764000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-1739000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-1715000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-1691000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-2394000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-1645000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5660,21 +7798,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-1764000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-1739000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-1715000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-1691000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-2394000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-1645000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5683,21 +7822,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-86923000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>166657000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>230982000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>89605000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>51571000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-246316000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5706,21 +7846,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-86923000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>166657000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>230982000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>89605000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>51571000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-246316000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5729,21 +7870,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-84604000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>167791000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>232660000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>90142000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>55214000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-220337000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5752,21 +7894,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>270518000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>249000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>232660000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>292310000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>198660000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>227584000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5775,21 +7918,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-355122000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-81209000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-202168000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-143446000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-447921000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5807,12 +7951,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="n">
         <v>-2032000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5830,12 +7975,13 @@
         <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
         <v>-2032000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5844,21 +7990,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-2319000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-1134000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-1678000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-537000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-1611000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-25979000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5867,21 +8014,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-2319000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-1134000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-1678000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-537000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-1611000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-25979000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5890,21 +8038,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>201631000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>179604000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>143510000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>72105000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>109929000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>50538000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5913,21 +8062,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>201631000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>179604000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>143510000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>72105000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>109929000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>50538000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5936,21 +8086,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>67577000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>13789000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>3968000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-26101000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>7597000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-71802000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5959,21 +8110,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-27625000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>82164000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>55441000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-3178000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-31852000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>24657000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5982,21 +8134,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-3180000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-1240000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-2840000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-4466000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-1049000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-3009000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6005,21 +8158,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>992000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-2931000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>1525000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-12593000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-12973000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6028,21 +8182,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-2306000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>22268000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>18518000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>17791000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-21831000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>1732000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6051,21 +8206,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-22802000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>16907000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>13525000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>16751000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-19353000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>2760000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6074,21 +8230,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>20496000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>5361000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>4993000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>1040000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-2478000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-1028000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6097,21 +8254,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>20496000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>5361000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>4993000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>1040000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-2478000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-1028000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6120,21 +8278,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-13388000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-9173000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>2773000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>317000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-4973000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-24231000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6143,21 +8302,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>112951000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-81222000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-66993000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-38090000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>79895000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-57978000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6166,21 +8326,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>112951000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-81222000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-66993000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-38090000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>79895000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-57978000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6192,10 +8353,11 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n">
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="H43" s="3" t="n">
         <v>715000</v>
       </c>
     </row>
@@ -6206,21 +8368,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>137830000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>143993000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>133630000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>140400000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>132431000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>125042000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6229,21 +8392,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>-1084000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-2094000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-2210000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>-2739000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>-3800000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-5942000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6252,21 +8416,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>-2471000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>447000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-1159000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>25000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-15995000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6275,21 +8440,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>-2471000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>447000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-1159000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>25000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>-15995000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6298,21 +8464,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>9127000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>9279000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>9562000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>9511000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>9060000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>6112000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6321,21 +8488,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>9127000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>9279000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>9562000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>9511000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>9060000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>6112000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6344,21 +8512,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>9127000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>9279000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>9562000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>9511000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>9060000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>6112000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6367,21 +8536,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>-16272000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>1578000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>120000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>-759000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>2242000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>-2703000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6390,21 +8560,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>-16420000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>291000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>272000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>253000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6413,21 +8584,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>148000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>1078000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>-171000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>-759000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>1970000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>-2956000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6436,28 +8608,29 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>15530000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>-2007000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>-47048000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>-37626000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>15826000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
